--- a/data/trans_orig/IP16A04-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP16A04-Provincia-trans_orig.xlsx
@@ -1423,7 +1423,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4982</t>
+          <t>4345</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>42,85%</t>
+          <t>37,37%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5062</t>
+          <t>4915</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>22,15%</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6645</t>
+          <t>7282</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>57,15%</t>
+          <t>62,63%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>17126</t>
+          <t>17273</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>77,19%</t>
+          <t>77,85%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1801,7 +1801,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4852</t>
+          <t>4718</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>28,72%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4781</t>
+          <t>4632</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,13%</t>
         </is>
       </c>
     </row>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>11574</t>
+          <t>11708</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>70,46%</t>
+          <t>71,28%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>27996</t>
+          <t>28145</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,41%</t>
+          <t>85,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2144,7 +2144,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2885</t>
+          <t>2894</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>36,89%</t>
+          <t>37,0%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2179,7 +2179,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4041</t>
+          <t>3565</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>21,04%</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4935</t>
+          <t>4926</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>63,11%</t>
+          <t>63,0%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2287,7 +2287,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>12906</t>
+          <t>13382</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>76,15%</t>
+          <t>78,96%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -3481,7 +3481,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>4994</t>
+          <t>4706</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>673</t>
+          <t>672</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>5186</t>
+          <t>6954</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1371</t>
+          <t>1373</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>8042</t>
+          <t>8220</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,05%</t>
         </is>
       </c>
     </row>
@@ -3589,7 +3589,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>120311</t>
+          <t>120599</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -3604,7 +3604,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>138733</t>
+          <t>136965</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>143246</t>
+          <t>143247</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3639,7 +3639,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>261182</t>
+          <t>261004</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>267853</t>
+          <t>267851</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -4095,7 +4095,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3910</t>
+          <t>3373</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4110,7 +4110,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4130,7 +4130,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3173</t>
+          <t>3976</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>9,11%</t>
         </is>
       </c>
     </row>
@@ -4203,7 +4203,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>20673</t>
+          <t>21210</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -4218,7 +4218,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,09%</t>
+          <t>86,28%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4238,7 +4238,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>40471</t>
+          <t>39668</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -4253,7 +4253,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>90,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4403,7 +4403,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3276</t>
+          <t>2582</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4418,7 +4418,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2756</t>
+          <t>3108</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4473,7 +4473,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4302</t>
+          <t>4309</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4488,7 +4488,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,13%</t>
         </is>
       </c>
     </row>
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>29671</t>
+          <t>30365</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -4526,7 +4526,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,06%</t>
+          <t>92,16%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>34538</t>
+          <t>34186</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -4561,7 +4561,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>91,67%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>65939</t>
+          <t>65932</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>93,87%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3069</t>
+          <t>3218</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6511,7 +6511,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6531,7 +6531,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3043</t>
+          <t>3166</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6546,7 +6546,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>6,18%</t>
         </is>
       </c>
     </row>
@@ -6604,7 +6604,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>23835</t>
+          <t>23686</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -6619,7 +6619,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>88,59%</t>
+          <t>88,04%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -6639,7 +6639,7 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>48212</t>
+          <t>48089</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
@@ -6654,7 +6654,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -6804,7 +6804,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>3177</t>
+          <t>3130</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6819,7 +6819,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>605</t>
+          <t>602</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>5577</t>
+          <t>5531</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6849,12 +6849,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6869,12 +6869,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>628</t>
+          <t>629</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>6243</t>
+          <t>5706</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6889,7 +6889,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
@@ -6912,7 +6912,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>183815</t>
+          <t>183862</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>185901</t>
+          <t>185947</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>190873</t>
+          <t>190876</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6962,12 +6962,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,69%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6982,12 +6982,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>372227</t>
+          <t>372764</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>377842</t>
+          <t>377841</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6997,7 +6997,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -7383,7 +7383,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3428</t>
+          <t>3183</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7398,7 +7398,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7453,7 +7453,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4196</t>
+          <t>2935</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7468,7 +7468,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>6,66%</t>
         </is>
       </c>
     </row>
@@ -7491,7 +7491,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16127</t>
+          <t>16372</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -7506,7 +7506,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>82,47%</t>
+          <t>83,72%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -7561,7 +7561,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>39860</t>
+          <t>41121</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -7576,7 +7576,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,48%</t>
+          <t>93,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -7761,7 +7761,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3586</t>
+          <t>4147</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7776,7 +7776,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7796,7 +7796,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3623</t>
+          <t>4498</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7811,7 +7811,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>8,37%</t>
         </is>
       </c>
     </row>
@@ -7869,7 +7869,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>19732</t>
+          <t>19171</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -7884,7 +7884,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,62%</t>
+          <t>82,21%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -7904,7 +7904,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>50108</t>
+          <t>49233</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -7919,7 +7919,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,26%</t>
+          <t>91,63%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -8069,7 +8069,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3485</t>
+          <t>3067</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8084,7 +8084,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>33,87%</t>
+          <t>29,82%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8139,7 +8139,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5059</t>
+          <t>4006</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8154,7 +8154,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>20,01%</t>
         </is>
       </c>
     </row>
@@ -8177,7 +8177,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6802</t>
+          <t>7220</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -8192,7 +8192,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>66,13%</t>
+          <t>70,18%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -8247,7 +8247,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>14955</t>
+          <t>16008</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -8262,7 +8262,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>74,72%</t>
+          <t>79,99%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -8412,7 +8412,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2594</t>
+          <t>2776</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8427,7 +8427,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8482,7 +8482,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2995</t>
+          <t>2719</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8497,7 +8497,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,21%</t>
         </is>
       </c>
     </row>
@@ -8520,7 +8520,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>32321</t>
+          <t>32139</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -8535,7 +8535,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>92,05%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -8590,7 +8590,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>61532</t>
+          <t>61808</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -8605,7 +8605,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -9441,7 +9441,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4436</t>
+          <t>4647</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9456,7 +9456,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9476,7 +9476,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3079</t>
+          <t>2815</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9491,7 +9491,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9506,12 +9506,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>654</t>
+          <t>656</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5857</t>
+          <t>5882</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9521,12 +9521,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>17,47%</t>
         </is>
       </c>
     </row>
@@ -9549,7 +9549,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>15277</t>
+          <t>15066</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -9564,7 +9564,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>77,5%</t>
+          <t>76,43%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -9584,7 +9584,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>10885</t>
+          <t>11149</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -9599,7 +9599,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>77,95%</t>
+          <t>79,84%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -9619,12 +9619,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>27820</t>
+          <t>27795</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>33023</t>
+          <t>33021</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9634,12 +9634,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>82,61%</t>
+          <t>82,53%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,05%</t>
         </is>
       </c>
     </row>
@@ -9784,7 +9784,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2689</t>
+          <t>2505</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9799,7 +9799,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9854,7 +9854,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3035</t>
+          <t>3049</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9869,7 +9869,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,12%</t>
         </is>
       </c>
     </row>
@@ -9892,7 +9892,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>26605</t>
+          <t>26789</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -9907,7 +9907,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>90,82%</t>
+          <t>91,45%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -9962,7 +9962,7 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>56526</t>
+          <t>56512</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
@@ -9977,7 +9977,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -10122,12 +10122,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1836</t>
+          <t>1497</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>8510</t>
+          <t>8050</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10137,12 +10137,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10162,7 +10162,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>4940</t>
+          <t>4695</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10177,7 +10177,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10192,12 +10192,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2576</t>
+          <t>2575</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>10070</t>
+          <t>10557</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10212,7 +10212,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,4%</t>
         </is>
       </c>
     </row>
@@ -10235,12 +10235,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>154026</t>
+          <t>154486</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>160700</t>
+          <t>161039</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10250,12 +10250,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10270,7 +10270,7 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>143185</t>
+          <t>143430</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
@@ -10285,7 +10285,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -10305,12 +10305,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>300591</t>
+          <t>300104</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>308085</t>
+          <t>308086</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10320,7 +10320,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">

--- a/data/trans_orig/IP16A04-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP16A04-Provincia-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -835,47 +835,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>12135</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>11668</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>12135</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -948,57 +948,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>12135</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>12135</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>12135</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>11668</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>11668</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>11668</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>12135</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>12135</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>12135</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1178,47 +1178,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>19856</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>16730</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>19856</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1291,57 +1291,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>19856</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>19856</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>19856</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>16730</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>16730</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>16730</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>19856</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>19856</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>19856</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1408,107 +1408,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>1436</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4345</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>4920</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>12,35%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>37,37%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>42,31%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>1436</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>4908</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>6,47%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>1436</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>4915</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>6,47%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>22,12%</t>
         </is>
       </c>
     </row>
@@ -1521,74 +1521,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>10561</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>10191</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>7282</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>6707</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>11627</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>87,65%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>62,63%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>57,69%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>10561</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>31</t>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>17273</t>
+          <t>17280</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>77,85%</t>
+          <t>77,88%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1634,57 +1634,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>10561</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>10561</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>10561</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>11627</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>11627</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>11627</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>10561</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>10561</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>10561</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1751,107 +1751,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1486</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4460</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
+          <t>9,05%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>27,15%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>1486</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>4718</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>9,05%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>4640</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>4,53%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>28,72%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1486</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>4632</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>4,53%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>14,16%</t>
         </is>
       </c>
     </row>
@@ -1864,72 +1864,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>14940</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>11966</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>16426</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>90,95%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>72,85%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>16351</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>14940</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>11708</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>16426</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>90,95%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>71,28%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>28145</t>
+          <t>28137</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,87%</t>
+          <t>85,84%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -1977,57 +1977,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>16426</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>16426</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>16426</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>16351</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>16351</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>16351</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>16426</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>16426</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>16426</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2094,107 +2094,107 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>698</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2901</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
+          <t>8,93%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>37,1%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>698</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>2894</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>8,93%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>3341</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>4,12%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>37,0%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>698</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>3565</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>4,12%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>19,72%</t>
         </is>
       </c>
     </row>
@@ -2207,72 +2207,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>7122</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>4919</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>7820</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>91,07%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>62,9%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>9126</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>7122</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>4926</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>7820</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>91,07%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>63,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,7 +2287,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>13382</t>
+          <t>13606</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>78,96%</t>
+          <t>80,28%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2320,57 +2320,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>7820</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>7820</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>7820</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>9126</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>9126</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>9126</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>7820</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>7820</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>7820</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2550,47 +2550,47 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>10729</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>12379</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>10729</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -2663,57 +2663,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>10729</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>10729</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>10729</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>12379</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>12379</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>12379</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>10729</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>10729</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>10729</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2893,47 +2893,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>26526</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>21499</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>26526</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -3006,57 +3006,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>26526</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>26526</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>26526</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>21499</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>21499</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>21499</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>26526</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>26526</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>26526</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3236,47 +3236,47 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>39867</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>25924</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>39867</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -3349,57 +3349,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>39867</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>39867</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>39867</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>25924</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>25924</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>25924</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>39867</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>39867</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>39867</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3466,72 +3466,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>2184</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>670</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>6599</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>1,52%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>0,47%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>4,59%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr">
         <is>
           <t>1436</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>4706</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>5206</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
         <is>
           <t>1,15%</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="O28" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>3,76%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>2184</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>672</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>6954</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>1,52%</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1373</t>
+          <t>1366</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>8220</t>
+          <t>7249</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,69%</t>
         </is>
       </c>
     </row>
@@ -3579,74 +3579,74 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>141735</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>137320</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>143249</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>98,48%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>95,41%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>99,53%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>188</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="K29" s="2" t="inlineStr">
         <is>
           <t>123869</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>120599</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>120099</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
         <is>
           <t>125305</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="N29" s="2" t="inlineStr">
         <is>
           <t>98,85%</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>96,24%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>95,85%</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>141735</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>136965</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>143247</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>98,48%</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>95,17%</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>99,53%</t>
-        </is>
-      </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
           <t>400</t>
@@ -3659,12 +3659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>261004</t>
+          <t>261975</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>267851</t>
+          <t>267858</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -3692,57 +3692,57 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>143919</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>143919</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>143919</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>190</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
         <is>
           <t>125305</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="L30" s="2" t="inlineStr">
         <is>
           <t>125305</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="M30" s="2" t="inlineStr">
         <is>
           <t>125305</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>143919</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>143919</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>143919</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3866,7 +3866,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3877,7 +3877,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4045,107 +4045,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>641</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3366</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
+          <t>2,61%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>641</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>3373</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>2,61%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>3162</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>1,47%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>13,72%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>641</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>3976</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>1,47%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>7,24%</t>
         </is>
       </c>
     </row>
@@ -4158,72 +4158,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>23942</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>21217</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>24583</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>97,39%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>86,31%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>19060</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>23942</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>21210</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>24583</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>97,39%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,28%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4238,7 +4238,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>39668</t>
+          <t>40482</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -4253,7 +4253,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,89%</t>
+          <t>92,76%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4271,57 +4271,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>24583</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>24583</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>24583</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>19060</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>19060</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>19060</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>24583</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>24583</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>24583</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4393,102 +4393,102 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>607</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>2962</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,63%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>7,94%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
           <t>627</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>2582</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3220</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>1,9%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>7,84%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>607</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>3108</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,63%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>9,77%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>4446</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>1,76%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>8,33%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>1234</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>4309</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>1,76%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,33%</t>
         </is>
       </c>
     </row>
@@ -4501,74 +4501,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>36687</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>34332</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>37294</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>98,37%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>92,06%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>48</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>32320</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>30365</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>29727</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>32947</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>98,1%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>92,16%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>90,23%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>36687</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>34186</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>37294</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>98,37%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>91,67%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>103</t>
@@ -4581,7 +4581,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>65932</t>
+          <t>65795</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4614,57 +4614,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>37294</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>37294</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>37294</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>49</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>32947</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>32947</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>32947</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>37294</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>37294</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>37294</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4844,47 +4844,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>23658</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>19276</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>23658</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -4957,57 +4957,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>23658</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>23658</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>23658</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>19276</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>19276</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>19276</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>23658</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>23658</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>23658</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5187,47 +5187,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>16750</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>24892</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>16750</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -5300,57 +5300,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>16750</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>16750</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>16750</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>24892</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>24892</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>24892</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>16750</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>16750</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>16750</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5530,47 +5530,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>13587</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>19813</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>13587</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -5643,57 +5643,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>13587</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>13587</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>13587</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>19813</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>19813</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>19813</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>13587</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>13587</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>13587</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5873,47 +5873,47 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>19510</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>13142</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>19510</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -5986,57 +5986,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>19510</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>19510</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>19510</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>13142</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>13142</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>13142</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>19510</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>19510</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>19510</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6216,47 +6216,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>29191</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>33511</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>29191</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -6329,57 +6329,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>29191</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>29191</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>29191</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>33511</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>33511</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>33511</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>29191</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>29191</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>29191</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6446,107 +6446,107 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>625</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3841</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
+          <t>2,32%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K25" s="2" t="inlineStr">
+      <c r="R25" s="2" t="inlineStr">
         <is>
           <t>625</t>
         </is>
       </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>3218</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>2,32%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>2547</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>1,22%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>11,96%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>625</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>3166</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>1,22%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>4,97%</t>
         </is>
       </c>
     </row>
@@ -6559,72 +6559,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>26279</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>23063</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>26904</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>97,68%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>85,72%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>24350</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>26279</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>23686</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>26904</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>97,68%</t>
-        </is>
-      </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>88,04%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6639,7 +6639,7 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>48089</t>
+          <t>48708</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
@@ -6654,7 +6654,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>95,03%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -6672,57 +6672,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>26904</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>26904</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>26904</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>24350</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>24350</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>24350</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>26904</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>26904</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>26904</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6789,72 +6789,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>1873</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>608</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>5694</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>0,98%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>0,32%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>2,97%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr">
         <is>
           <t>627</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>3130</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>3177</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
         <is>
           <t>0,34%</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="O28" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>1,67%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>1873</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>602</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>5531</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>0,98%</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>0,31%</t>
-        </is>
-      </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6869,12 +6869,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>629</t>
+          <t>624</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5706</t>
+          <t>6247</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6884,12 +6884,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,65%</t>
         </is>
       </c>
     </row>
@@ -6907,69 +6907,69 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
+          <t>189605</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>185784</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>190870</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>99,02%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>97,03%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>99,68%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>268</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
           <t>186365</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>183862</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>183815</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
         <is>
           <t>186992</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="N29" s="2" t="inlineStr">
         <is>
           <t>99,66%</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>98,33%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>98,3%</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>268</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>189605</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>185947</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>190876</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>99,02%</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>97,11%</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>99,69%</t>
-        </is>
-      </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
           <t>536</t>
@@ -6982,12 +6982,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>372764</t>
+          <t>372223</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>377841</t>
+          <t>377846</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6997,12 +6997,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>99,83%</t>
+          <t>99,84%</t>
         </is>
       </c>
     </row>
@@ -7015,57 +7015,57 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>271</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>191478</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>191478</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>191478</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>269</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
         <is>
           <t>186992</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="L30" s="2" t="inlineStr">
         <is>
           <t>186992</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="M30" s="2" t="inlineStr">
         <is>
           <t>186992</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>271</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>191478</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>191478</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>191478</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7189,7 +7189,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -7200,7 +7200,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -7368,107 +7368,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>617</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3183</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3673</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>3,16%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>16,28%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>18,78%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>617</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>3097</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>1,4%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>617</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>2935</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>1,4%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>7,03%</t>
         </is>
       </c>
     </row>
@@ -7481,74 +7481,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>24501</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>18938</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>16372</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>15882</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>19555</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>96,84%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>83,72%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>81,22%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>24501</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>64</t>
@@ -7561,7 +7561,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>41121</t>
+          <t>40959</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -7576,7 +7576,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>92,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -7594,57 +7594,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>24501</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>24501</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>24501</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>19555</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>19555</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>19555</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>24501</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>24501</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>24501</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7711,107 +7711,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>717</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
+          <t>3,08%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>717</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>4147</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>3,08%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>4061</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>1,33%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>17,79%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>717</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>4498</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>1,33%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>7,56%</t>
         </is>
       </c>
     </row>
@@ -7824,72 +7824,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>22601</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>19653</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>23318</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>96,92%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>84,28%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>30413</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>22601</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>19171</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>23318</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>96,92%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,21%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7904,7 +7904,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>49233</t>
+          <t>49670</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -7919,7 +7919,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,63%</t>
+          <t>92,44%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -7937,57 +7937,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>23318</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>23318</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>23318</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>30413</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>30413</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>30413</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>23318</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>23318</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>23318</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8054,107 +8054,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>727</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>3067</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>3497</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>7,07%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>29,82%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>34,0%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>727</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>4082</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>3,63%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>727</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>4006</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>3,63%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>20,4%</t>
         </is>
       </c>
     </row>
@@ -8172,69 +8172,69 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>9727</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
           <t>9560</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>7220</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>6790</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>10287</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>92,93%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>70,18%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>66,0%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>9727</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>28</t>
@@ -8247,7 +8247,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>16008</t>
+          <t>15932</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -8262,7 +8262,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>79,99%</t>
+          <t>79,6%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -8280,57 +8280,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>9727</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>9727</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>9727</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>10287</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>10287</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>10287</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>9727</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>9727</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>9727</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8397,107 +8397,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>536</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>2776</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>2777</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>1,53%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
         <is>
           <t>7,95%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>536</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>2229</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,83%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>536</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>2719</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,83%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>3,45%</t>
         </is>
       </c>
     </row>
@@ -8510,74 +8510,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>29612</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>34379</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>32139</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>32138</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>34915</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>98,47%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>92,05%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>29612</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>90</t>
@@ -8590,7 +8590,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>61808</t>
+          <t>62298</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -8605,7 +8605,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -8623,57 +8623,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>29612</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>29612</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>29612</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>51</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>34915</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>34915</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>34915</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>29612</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>29612</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>29612</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8858,42 +8858,42 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
+          <t>7262</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
           <t>7779</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>7262</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -8971,52 +8971,52 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
+          <t>7262</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>7262</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>7262</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
           <t>7779</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>7779</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>7779</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>7262</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>7262</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>7262</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9196,47 +9196,47 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>9475</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>10580</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>9475</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -9309,57 +9309,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>9475</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>9475</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>9475</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>10580</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>10580</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>10580</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>9475</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>9475</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>9475</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9426,72 +9426,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>652</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>3323</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>4,67%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>23,79%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>1542</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>4647</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>5960</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>7,82%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>23,57%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>652</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>2815</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>4,67%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>30,23%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9506,12 +9506,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>656</t>
+          <t>663</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5882</t>
+          <t>5121</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9521,12 +9521,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>15,21%</t>
         </is>
       </c>
     </row>
@@ -9539,74 +9539,74 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>13312</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>10641</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>13964</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>95,33%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>76,21%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>18171</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>15066</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>13753</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>19713</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>92,18%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>76,43%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>69,77%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>13312</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>11149</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>13964</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>95,33%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>79,84%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
           <t>48</t>
@@ -9619,12 +9619,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>27795</t>
+          <t>28556</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>33021</t>
+          <t>33014</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9634,12 +9634,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>82,53%</t>
+          <t>84,79%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,03%</t>
         </is>
       </c>
     </row>
@@ -9652,57 +9652,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>13964</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>13964</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>13964</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>19713</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>19713</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>19713</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>13964</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>13964</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>13964</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9769,107 +9769,107 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>605</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>2505</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>2687</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>2,07%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="O25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>8,55%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>9,17%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>605</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>3057</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>1,02%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>605</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>3049</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>1,02%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,13%</t>
         </is>
       </c>
     </row>
@@ -9887,69 +9887,69 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
+          <t>30267</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
           <t>28689</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>26789</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>26607</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
         <is>
           <t>29294</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>97,93%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>91,45%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>90,83%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>30267</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
           <t>92</t>
@@ -9962,7 +9962,7 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>56512</t>
+          <t>56504</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
@@ -9977,7 +9977,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>94,87%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -9995,57 +9995,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>30267</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>30267</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>30267</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>29294</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>29294</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>29294</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>30267</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>30267</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>30267</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -10112,72 +10112,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>1370</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>4795</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>0,92%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>3,24%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr">
         <is>
           <t>4028</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>1497</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>8050</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>1461</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>8802</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
         <is>
           <t>2,48%</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>0,92%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>4,95%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>1370</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>4695</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>0,92%</t>
-        </is>
-      </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10192,12 +10192,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2575</t>
+          <t>2439</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>10557</t>
+          <t>9734</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10207,12 +10207,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,13%</t>
         </is>
       </c>
     </row>
@@ -10225,72 +10225,72 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>146755</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>143330</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>148125</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>99,08%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>96,76%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>239</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="K29" s="2" t="inlineStr">
         <is>
           <t>158508</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>154486</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>161039</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>153734</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>161075</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
         <is>
           <t>97,52%</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>95,05%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>99,08%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>213</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>146755</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>143430</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>148125</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>99,08%</t>
-        </is>
-      </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>94,58%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10305,12 +10305,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>300104</t>
+          <t>300927</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>308086</t>
+          <t>308222</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10320,12 +10320,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,21%</t>
         </is>
       </c>
     </row>
@@ -10338,57 +10338,57 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>148125</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>148125</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>148125</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>245</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
         <is>
           <t>162536</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="L30" s="2" t="inlineStr">
         <is>
           <t>162536</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="M30" s="2" t="inlineStr">
         <is>
           <t>162536</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>148125</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>148125</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>148125</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
